--- a/Task4/Расчет стоимости.xlsx
+++ b/Task4/Расчет стоимости.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sergej/Documents/GitHub/Solution-AI-Sprint7/Task4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9FD8A150-63F7-004E-939F-426002DF116F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1478525-A062-FB42-96D7-7753D99C770C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43540" yWindow="10340" windowWidth="28240" windowHeight="17240" xr2:uid="{3D5DA903-D285-2E43-B672-C71C9FDCA770}"/>
+    <workbookView xWindow="40180" yWindow="4900" windowWidth="31960" windowHeight="21880" xr2:uid="{3D5DA903-D285-2E43-B672-C71C9FDCA770}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>Допущение</t>
   </si>
@@ -104,10 +104,43 @@
     <t>ЧЧ на разработку и поддержку модели</t>
   </si>
   <si>
-    <t>Считаем среднее чч всех экспертов = 2к, т.е при разработке модели учитываем кол-во экспертов в размере 15ч и разработка в течении 1 месяца разработки - то сумма получается  750к на разработку, поддержку и тестирование</t>
-  </si>
-  <si>
     <t>По факту с приходом модели увеличится качество проверок сотрудниками и увеличится кол-во сдерживания клиентов. Что заметно улучшит отношение клиентов к банку</t>
+  </si>
+  <si>
+    <t>Интеграция</t>
+  </si>
+  <si>
+    <t>Комментарий</t>
+  </si>
+  <si>
+    <t>Ручная проверка</t>
+  </si>
+  <si>
+    <t>Эксплуатация</t>
+  </si>
+  <si>
+    <t>Возьмем в размере 20 тысяч в месяц</t>
+  </si>
+  <si>
+    <t>Расчеты в формате "Пальцем в небо"</t>
+  </si>
+  <si>
+    <t>Поддержка интеграции - 30 тысяч</t>
+  </si>
+  <si>
+    <t>Проверка в рамках пилота - 3 месяца. Если разбор случаев составляет больше 30к операций в месяц - успех (по факту успех должен определять бизнес). Если приостановок в месяц дошли до 100 в месяц - успех пилота</t>
+  </si>
+  <si>
+    <t>Сумма в первый год</t>
+  </si>
+  <si>
+    <t>Сумма во второй год</t>
+  </si>
+  <si>
+    <t>Считаем среднее чч всех экспертов = 2к, т.е при разработке модели учитываем кол-во экспертов в размере 15ч и разработка в течении 1 месяца разработки - то сумма получается  750к на разработку, поддержку модели</t>
+  </si>
+  <si>
+    <t>Аналогично эксплуатациии - 30 тысяч в месяц на 1 сотрудника</t>
   </si>
 </sst>
 </file>
@@ -139,7 +172,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -162,11 +195,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -177,7 +230,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -512,7 +581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8D4CBAD-2023-5F43-8E3D-4AA6815D2554}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.6640625" customWidth="1"/>
@@ -584,11 +653,14 @@
       <c r="D6" s="5"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="1" t="s">
         <v>17</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="51" x14ac:dyDescent="0.2">
@@ -607,22 +679,84 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="153" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="8"/>
+    </row>
+    <row r="12" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="8"/>
+    </row>
+    <row r="13" spans="1:4" ht="136" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B13" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="12">
+        <v>10350000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="12">
+        <v>9600000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="7"/>
+      <c r="B16" s="10"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="7"/>
+    </row>
+    <row r="18" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>23</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="A6:D6"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="A18:D18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Task4/Расчет стоимости.xlsx
+++ b/Task4/Расчет стоимости.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sergej/Documents/GitHub/Solution-AI-Sprint7/Task4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1478525-A062-FB42-96D7-7753D99C770C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA15225-F7F5-5646-8639-3A72B3E7B967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="40180" yWindow="4900" windowWidth="31960" windowHeight="21880" xr2:uid="{3D5DA903-D285-2E43-B672-C71C9FDCA770}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="52">
   <si>
     <t>Допущение</t>
   </si>
@@ -83,71 +83,122 @@
     <t>Расчет стоимости</t>
   </si>
   <si>
-    <t>С внедрением модели планируется уменьшить кол-во сигналов для разбора в 2 раза, т.е 5 тысяч сигналов в месяц</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Качество проверок сотрудниками вырастет в связи со снижением нагрузки </t>
-  </si>
-  <si>
-    <t>Сумма</t>
-  </si>
-  <si>
     <t>Внедрение модели</t>
   </si>
   <si>
-    <t>35 тысяч запросов в месяц - небольшое кол-во (1 запрос в минуту), т.е покупать собственное железо на своем ЦОД не вижу смысла, проще реализовать гибридный закрытый контур</t>
-  </si>
-  <si>
-    <t>35 тысяч операций в месяц по API будут стоить примерно 3000-7000 рублей в месяц</t>
-  </si>
-  <si>
-    <t>ЧЧ на разработку и поддержку модели</t>
-  </si>
-  <si>
-    <t>По факту с приходом модели увеличится качество проверок сотрудниками и увеличится кол-во сдерживания клиентов. Что заметно улучшит отношение клиентов к банку</t>
-  </si>
-  <si>
-    <t>Интеграция</t>
-  </si>
-  <si>
-    <t>Комментарий</t>
-  </si>
-  <si>
-    <t>Ручная проверка</t>
-  </si>
-  <si>
-    <t>Эксплуатация</t>
-  </si>
-  <si>
-    <t>Возьмем в размере 20 тысяч в месяц</t>
-  </si>
-  <si>
-    <t>Расчеты в формате "Пальцем в небо"</t>
-  </si>
-  <si>
-    <t>Поддержка интеграции - 30 тысяч</t>
-  </si>
-  <si>
-    <t>Проверка в рамках пилота - 3 месяца. Если разбор случаев составляет больше 30к операций в месяц - успех (по факту успех должен определять бизнес). Если приостановок в месяц дошли до 100 в месяц - успех пилота</t>
-  </si>
-  <si>
-    <t>Сумма в первый год</t>
-  </si>
-  <si>
-    <t>Сумма во второй год</t>
-  </si>
-  <si>
-    <t>Считаем среднее чч всех экспертов = 2к, т.е при разработке модели учитываем кол-во экспертов в размере 15ч и разработка в течении 1 месяца разработки - то сумма получается  750к на разработку, поддержку модели</t>
-  </si>
-  <si>
-    <t>Аналогично эксплуатациии - 30 тысяч в месяц на 1 сотрудника</t>
+    <t>Сумма на Пилот (3 месяца)</t>
+  </si>
+  <si>
+    <t>Первый год эксплуатации</t>
+  </si>
+  <si>
+    <t>Комментарий+</t>
+  </si>
+  <si>
+    <t>Data Engineering: пайплайны, feature store, исторические данные</t>
+  </si>
+  <si>
+    <t>3–6 млн ₽</t>
+  </si>
+  <si>
+    <t>1–2 млн ₽ / год</t>
+  </si>
+  <si>
+    <t>История операций, контрагенты, ОКВЭД, каналы, лимиты</t>
+  </si>
+  <si>
+    <t>ML-разработка: baseline, LightGBM, графовые признаки, калибровка</t>
+  </si>
+  <si>
+    <t>4–8 млн ₽</t>
+  </si>
+  <si>
+    <t>2–4 млн ₽ / год</t>
+  </si>
+  <si>
+    <t>Включая shadow mode и threshold tuning</t>
+  </si>
+  <si>
+    <t>MLOps и инфраструктура</t>
+  </si>
+  <si>
+    <t>2–4 млн ₽</t>
+  </si>
+  <si>
+    <t>2–5 млн ₽ / год</t>
+  </si>
+  <si>
+    <t>Реестр моделей, мониторинг, CI/CD, вычисления</t>
+  </si>
+  <si>
+    <t>Интеграция с case management и UI аналитика</t>
+  </si>
+  <si>
+    <t>2–5 млн ₽</t>
+  </si>
+  <si>
+    <t>Скор, объяснение, решение, аудит-лог</t>
+  </si>
+  <si>
+    <t>Комплаенс, валидация, юридическая проработка</t>
+  </si>
+  <si>
+    <t>1–3 млн ₽</t>
+  </si>
+  <si>
+    <t>Правила auto-close, модельный риск, процедуры</t>
+  </si>
+  <si>
+    <t>Информационная безопасность и DPO</t>
+  </si>
+  <si>
+    <t>0,5–2 млн ₽</t>
+  </si>
+  <si>
+    <t>0,5–1 млн ₽ / год</t>
+  </si>
+  <si>
+    <t>Доступы, псевдонимизация, аудит</t>
+  </si>
+  <si>
+    <t>Эксплуатация и поддержка</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>3–6 млн ₽ / год</t>
+  </si>
+  <si>
+    <t>Поддержка пайплайнов, дрейф, переобучение</t>
+  </si>
+  <si>
+    <t>Итого ориентировочно</t>
+  </si>
+  <si>
+    <t>12–28 млн ₽</t>
+  </si>
+  <si>
+    <t>10–22 млн ₽ / год</t>
+  </si>
+  <si>
+    <t>Без стоимости лицензий внешних вендоров</t>
+  </si>
+  <si>
+    <t>в AS IS обрабатывается только 29% входящего потока. Ежемесячно не разбирается 25 000 операций, а приоритизация по крупным суммам означает, что часть рисков меньшего размера системно остаётся вне контроля.</t>
+  </si>
+  <si>
+    <t>ML не сокращает «400 эскалаций» как самоцель. Его задача — снизить долю ложноположительных разборов и направить высвобожденную мощность на backlog, priority-кейсы и более глубокое расследование.</t>
+  </si>
+  <si>
+    <t>5% снижения false positives, 2 500 auto-close в месяц, 11,25 млн ₽ годовой экономии по ФОТ-эквиваленту, при обязательном условии отсутствия роста false negatives и сохранения human-in-the-loop для всех решений с регуляторными последствиями.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -163,6 +214,19 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -172,7 +236,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -195,31 +259,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -230,23 +274,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -581,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8D4CBAD-2023-5F43-8E3D-4AA6815D2554}">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.6640625" customWidth="1"/>
@@ -654,109 +687,161 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="6" t="s">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="51" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="85" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
+      <c r="C9" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="3" t="s">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="8" t="s">
         <v>27</v>
       </c>
+      <c r="B10" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="C10" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="8"/>
-    </row>
-    <row r="12" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="8"/>
-    </row>
-    <row r="13" spans="1:4" ht="136" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
+      <c r="B12" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="12">
-        <v>10350000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="12">
-        <v>9600000</v>
+      <c r="D12" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="7"/>
-      <c r="B16" s="10"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="7"/>
-    </row>
-    <row r="18" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>22</v>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A17:D17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
